--- a/loan_application_forms/023_employee_loan_application_request_form--loan_application_forms.xlsx
+++ b/loan_application_forms/023_employee_loan_application_request_form--loan_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Loan Term</t>
+          <t>Loan Term Options</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Loan Interest Rate</t>
+          <t>Loan Interest Rate Options</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manager Approval</t>
+          <t>Manager Approval Options</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'one_month'}</t>
+          <t>one_month</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'One Month'}</t>
+          <t>One Month</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'three_months'}</t>
+          <t>three_months</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Three Months'}</t>
+          <t>Three Months</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'six_months'}</t>
+          <t>six_months</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Six Months'}</t>
+          <t>Six Months</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'twelve_months'}</t>
+          <t>twelve_months</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Twelve Months'}</t>
+          <t>Twelve Months</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'5.5%'}</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '5.5%'}</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'6.5%'}</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '6.5%'}</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'7.5%'}</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '7.5%'}</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'8.5%'}</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '8.5%'}</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'9.5%'}</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '9.5%'}</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'5.5%'}</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '5.5%'}</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'6.5%'}</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '6.5%'}</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'7.5%'}</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '7.5%'}</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'8.5%'}</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '8.5%'}</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'9.5%'}</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': '9.5%'}</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'approve'}</t>
+          <t>approve</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Approve'}</t>
+          <t>Approve</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'disapprove'}</t>
+          <t>disapprove</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Disapprove'}</t>
+          <t>Disapprove</t>
         </is>
       </c>
     </row>
